--- a/public/plantillas/Plantilla Cursos Extension.xlsx
+++ b/public/plantillas/Plantilla Cursos Extension.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/Plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{0122E598-D09C-49DC-99A8-6EC15D2B76AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AF0CCBF-09E5-4DFE-A430-6AEAC10C041C}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="13_ncr:1_{0122E598-D09C-49DC-99A8-6EC15D2B76AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC98A1E4-E113-431C-95ED-34901945D689}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="244">
   <si>
     <t>Obligatorio</t>
   </si>
@@ -783,9 +783,6 @@
   </si>
   <si>
     <t>fechanacimiento2</t>
-  </si>
-  <si>
-    <t>FECHANACIMIENTO2</t>
   </si>
   <si>
     <t>Validación2</t>
@@ -1933,13 +1930,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2031,13 +2028,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2129,13 +2126,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2227,13 +2224,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2325,13 +2322,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2423,13 +2420,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2521,13 +2518,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
@@ -2603,13 +2600,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2685,13 +2682,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2767,13 +2764,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>792480</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2947,13 +2944,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -3234,118 +3231,12 @@
               </a:solidFill>
               <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>(Ejemplo: 6 de mayo de 2025)</a:t>
+            <a:t>(Opcional)</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO" sz="1100" b="0">
             <a:solidFill>
               <a:schemeClr val="bg1"/>
             </a:solidFill>
-            <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>546846</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>448234</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="CuadroTexto 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05F365B1-1E33-497B-B604-524AB6FFDC16}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10623176" y="546846"/>
-          <a:ext cx="1649506" cy="448235"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-CO" sz="1100" b="1">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>FECHA DE NACIMIENTO</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-CO" sz="1100" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>(Opcional)</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:effectLst/>
             <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
           </a:endParaRPr>
         </a:p>
@@ -3654,7 +3545,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A1:Z3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.296875" style="11" customWidth="1"/>
@@ -3666,25 +3557,24 @@
     <col min="7" max="7" width="21.59765625" style="8" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="8.3984375" style="3" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" style="3" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="25.8984375" style="3" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="22.3984375" style="3" customWidth="1"/>
     <col min="11" max="13" width="8.3984375" style="3" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="13.59765625" style="3" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="19.796875" style="11" customWidth="1"/>
     <col min="16" max="16" width="25.8984375" style="8" customWidth="1"/>
-    <col min="17" max="17" width="24.59765625" style="8" customWidth="1"/>
-    <col min="18" max="18" width="29.296875" style="8" customWidth="1"/>
-    <col min="19" max="19" width="19.796875" style="42" customWidth="1"/>
-    <col min="20" max="21" width="27.69921875" style="8" customWidth="1"/>
-    <col min="22" max="22" width="31.3984375" style="8" customWidth="1"/>
-    <col min="23" max="23" width="34" style="8" customWidth="1"/>
-    <col min="24" max="24" width="31.3984375" style="8" customWidth="1"/>
-    <col min="25" max="25" width="9.69921875" style="34" customWidth="1"/>
-    <col min="26" max="26" width="9.69921875" style="38" customWidth="1"/>
-    <col min="27" max="27" width="9.69921875" style="22" customWidth="1"/>
-    <col min="28" max="16384" width="10.5" style="3"/>
+    <col min="17" max="17" width="29.296875" style="8" customWidth="1"/>
+    <col min="18" max="18" width="19.796875" style="42" customWidth="1"/>
+    <col min="19" max="20" width="27.69921875" style="8" customWidth="1"/>
+    <col min="21" max="21" width="31.3984375" style="8" customWidth="1"/>
+    <col min="22" max="22" width="34" style="8" customWidth="1"/>
+    <col min="23" max="23" width="31.3984375" style="8" customWidth="1"/>
+    <col min="24" max="24" width="9.69921875" style="34" customWidth="1"/>
+    <col min="25" max="25" width="9.69921875" style="38" customWidth="1"/>
+    <col min="26" max="26" width="9.69921875" style="22" customWidth="1"/>
+    <col min="27" max="16384" width="10.5" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -3733,41 +3623,38 @@
       <c r="P1" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="Q1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="R1" s="16" t="s">
+      <c r="Q1" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="S1" s="39" t="s">
+      <c r="R1" s="39" t="s">
         <v>215</v>
       </c>
+      <c r="S1" s="16" t="s">
+        <v>214</v>
+      </c>
       <c r="T1" s="16" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="U1" s="16" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="V1" s="16" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="W1" s="16" t="s">
-        <v>216</v>
-      </c>
-      <c r="X1" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="Y1" s="31" t="s">
+      <c r="X1" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="Z1" s="35" t="s">
+      <c r="Y1" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="AA1" s="20" t="s">
+      <c r="Z1" s="20" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>3</v>
       </c>
@@ -3816,41 +3703,38 @@
       <c r="P2" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="Q2" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="R2" s="17" t="s">
+      <c r="Q2" s="17" t="s">
         <v>229</v>
       </c>
-      <c r="S2" s="40" t="s">
+      <c r="R2" s="40" t="s">
         <v>223</v>
       </c>
+      <c r="S2" s="17" t="s">
+        <v>222</v>
+      </c>
       <c r="T2" s="17" t="s">
-        <v>222</v>
-      </c>
-      <c r="U2" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="V2" s="8" t="s">
+      <c r="U2" s="8" t="s">
         <v>230</v>
       </c>
+      <c r="V2" s="17" t="s">
+        <v>224</v>
+      </c>
       <c r="W2" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="X2" s="17" t="s">
         <v>225</v>
       </c>
-      <c r="Y2" s="32" t="s">
+      <c r="X2" s="32" t="s">
         <v>227</v>
       </c>
-      <c r="Z2" s="36" t="s">
+      <c r="Y2" s="36" t="s">
         <v>226</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="Z2" s="21" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="23"/>
       <c r="B3" s="24"/>
       <c r="C3" s="50"/>
@@ -3868,20 +3752,20 @@
       <c r="O3" s="28"/>
       <c r="P3" s="24"/>
       <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="S3" s="24"/>
       <c r="T3" s="24"/>
       <c r="U3" s="24"/>
       <c r="V3" s="24"/>
       <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="33"/>
-      <c r="Z3" s="37"/>
-      <c r="AA3" s="29"/>
+      <c r="X3" s="33"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="29"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="PRMvY2+6YOb4MZLI9FfMT2qG2O2qECm8dKSKq0pZtexYn/0As7WhPt7pnbAKpU/LqXoo+Xb7VtEjg/QK5MkhQg==" saltValue="2saVmi/xgknDRn2a4eDSZA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange sqref="A3:AA422" name="Rango1"/>
+    <protectedRange sqref="A3:Z422" name="Rango1"/>
   </protectedRanges>
   <conditionalFormatting sqref="O3:O1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
@@ -3893,7 +3777,7 @@
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Parameters!$F$4:$F$5</xm:f>
@@ -3941,7 +3825,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="44" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">

--- a/public/plantillas/Plantilla Cursos Extension.xlsx
+++ b/public/plantillas/Plantilla Cursos Extension.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/Plantillas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\planeacionenap\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="13_ncr:1_{0122E598-D09C-49DC-99A8-6EC15D2B76AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC98A1E4-E113-431C-95ED-34901945D689}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE3F1F2-2E59-4501-AE47-5CBC6DFB2426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1119,7 +1119,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1263,7 +1263,6 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3550,8 +3549,8 @@
   <cols>
     <col min="1" max="1" width="25.296875" style="11" customWidth="1"/>
     <col min="2" max="2" width="25.296875" style="8" customWidth="1"/>
-    <col min="3" max="3" width="24" style="52" customWidth="1"/>
-    <col min="4" max="4" width="33.796875" style="52" customWidth="1"/>
+    <col min="3" max="3" width="24" style="51" customWidth="1"/>
+    <col min="4" max="4" width="33.796875" style="51" customWidth="1"/>
     <col min="5" max="5" width="28.3984375" style="3" customWidth="1"/>
     <col min="6" max="6" width="21.8984375" style="15" customWidth="1"/>
     <col min="7" max="7" width="21.59765625" style="8" hidden="1" customWidth="1"/>
@@ -3738,7 +3737,6 @@
       <c r="A3" s="23"/>
       <c r="B3" s="24"/>
       <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
       <c r="E3" s="30"/>
       <c r="F3" s="26"/>
       <c r="G3" s="24"/>
@@ -3763,7 +3761,7 @@
       <c r="Z3" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="PRMvY2+6YOb4MZLI9FfMT2qG2O2qECm8dKSKq0pZtexYn/0As7WhPt7pnbAKpU/LqXoo+Xb7VtEjg/QK5MkhQg==" saltValue="2saVmi/xgknDRn2a4eDSZA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="yBE3/x8hlpSNnnAkU+Ut1BahMoGQbgbJGzBfxkN3AgWwUDK60+S8P/J1ZMAsVepG1qaB6GwoDLN8q7TQEsTqOA==" saltValue="9sNR2iJDp+80bsxTGeG8+w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="A3:Z422" name="Rango1"/>
   </protectedRanges>
@@ -3777,7 +3775,7 @@
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Parameters!$F$4:$F$5</xm:f>
@@ -3829,8 +3827,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D3" s="1" t="s">
